--- a/data/trans_orig/P1805_2016_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1805_2016_2023-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,82 +746,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>42525</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30527</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>57875</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>58462</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>44761</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>76460</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42525</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29508</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>56699</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>58462</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>44257</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>75200</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>729139</t>
+          <t>728709</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>745580</t>
+          <t>744986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,82 +859,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>952135</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>936785</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>964133</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1601</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1690545</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1672547</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1704246</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>96,66%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>952135</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>937961</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>965152</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1601</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1690545</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1673807</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1704750</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>26073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>50291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58368</t>
+          <t>57301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92680</t>
+          <t>93693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90710</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134262</t>
+          <t>131754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026390</t>
+          <t>2026094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2050016</t>
+          <t>2050312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1895620</t>
+          <t>1894607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1929932</t>
+          <t>1930999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3930423</t>
+          <t>3932931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3973975</t>
+          <t>3974840</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>24498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34301</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531442</t>
+          <t>530312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543022</t>
+          <t>542910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525331</t>
+          <t>524642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540086</t>
+          <t>540142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1061726</t>
+          <t>1061895</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1081174</t>
+          <t>1080890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46442</t>
+          <t>46790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77803</t>
+          <t>77224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109658</t>
+          <t>110045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155162</t>
+          <t>156777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167139</t>
+          <t>167894</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225001</t>
+          <t>225615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3299815</t>
+          <t>3300394</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3331176</t>
+          <t>3330828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3376938</t>
+          <t>3375323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3422442</t>
+          <t>3422055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6684717</t>
+          <t>6684103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6742579</t>
+          <t>6741824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>34171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37711</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>30357</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50911</t>
+          <t>52650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>501343</t>
+          <t>564417</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>491033</t>
+          <t>554850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>507178</t>
+          <t>570928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>730826</t>
+          <t>795665</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>722961</t>
+          <t>787271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>737832</t>
+          <t>802446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1232170</t>
+          <t>1360082</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1218970</t>
+          <t>1347321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1240757</t>
+          <t>1369614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70613</t>
+          <t>75577</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47377</t>
+          <t>56768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95124</t>
+          <t>100929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78638</t>
+          <t>86423</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55288</t>
+          <t>70481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99623</t>
+          <t>106113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>149251</t>
+          <t>162000</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114237</t>
+          <t>138562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182340</t>
+          <t>192969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2219714</t>
+          <t>2154989</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2195203</t>
+          <t>2129637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2242950</t>
+          <t>2173798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2158507</t>
+          <t>2084284</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2137522</t>
+          <t>2064594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2181857</t>
+          <t>2100226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4378221</t>
+          <t>4239274</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4345132</t>
+          <t>4208305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4413235</t>
+          <t>4262712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,32 +3015,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42056</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>35007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54238</t>
+          <t>60036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68773</t>
+          <t>72469</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>56911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88545</t>
+          <t>91679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -3128,32 +3128,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>619907</t>
+          <t>684111</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604420</t>
+          <t>669133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628481</t>
+          <t>693916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3163,32 +3163,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>618407</t>
+          <t>689884</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>606225</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>629609</t>
+          <t>699870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1238313</t>
+          <t>1373995</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1218541</t>
+          <t>1354785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1252327</t>
+          <t>1389553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82228</t>
+          <t>92455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140464</t>
+          <t>144846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113595</t>
+          <t>135049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171157</t>
+          <t>183993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>274357</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216167</t>
+          <t>243679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294640</t>
+          <t>310319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3340965</t>
+          <t>3403518</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3311425</t>
+          <t>3375837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3369661</t>
+          <t>3428228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3507740</t>
+          <t>3569834</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3481393</t>
+          <t>3543033</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3538955</t>
+          <t>3591977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6848705</t>
+          <t>6973352</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6809799</t>
+          <t>6937390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6888272</t>
+          <t>7004030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
